--- a/assets/database_structure/owner_list.xlsx
+++ b/assets/database_structure/owner_list.xlsx
@@ -32,7 +32,7 @@
     <t>owner_name</t>
   </si>
   <si>
-    <t>onwer_email</t>
+    <t>owner_email</t>
   </si>
   <si>
     <t>owner_phone</t>
